--- a/academias/Química - Estadisticos 20221.xlsx
+++ b/academias/Química - Estadisticos 20221.xlsx
@@ -560,13 +560,13 @@
         <v>38.24</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1">
-        <v>32.35</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1401,13 +1401,13 @@
         <v>38.24</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1">
-        <v>32.35</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/academias/Química - Estadisticos 20221.xlsx
+++ b/academias/Química - Estadisticos 20221.xlsx
@@ -513,25 +513,25 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>58.97</v>
+        <v>82.05</v>
       </c>
       <c r="H2" s="1">
-        <v>41.03</v>
+        <v>17.95</v>
       </c>
       <c r="I2" s="2">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -548,25 +548,25 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>61.76</v>
+        <v>97.06</v>
       </c>
       <c r="H3" s="1">
-        <v>38.24</v>
+        <v>2.94</v>
       </c>
       <c r="I3" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -583,25 +583,25 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>75.61</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>24.39</v>
+        <v>9.76</v>
       </c>
       <c r="I4" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -615,28 +615,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>78.05</v>
+        <v>90</v>
       </c>
       <c r="H5" s="1">
-        <v>21.95</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -653,25 +653,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H6" s="1">
-        <v>8.33</v>
+        <v>2.78</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -720,19 +720,19 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>26</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H8" s="1">
-        <v>16.13</v>
+        <v>13.33</v>
       </c>
       <c r="I8" s="2">
         <v>6.9</v>
@@ -860,22 +860,22 @@
         <v>24</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12">
         <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>83.33</v>
+        <v>83.72</v>
       </c>
       <c r="H12" s="1">
-        <v>16.67</v>
+        <v>16.28</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -950,22 +950,25 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>82.05</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>17.95</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -982,22 +985,25 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1043,25 +1049,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1078,22 +1087,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>97.22</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>2.78</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1139,13 +1151,13 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1154,7 +1166,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1267,13 +1279,13 @@
         <v>24</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1282,7 +1294,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1354,25 +1366,25 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>58.97</v>
+        <v>82.05</v>
       </c>
       <c r="H2" s="1">
-        <v>41.03</v>
+        <v>17.95</v>
       </c>
       <c r="I2" s="2">
-        <v>8.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>41.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1389,25 +1401,25 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>61.76</v>
+        <v>94.12</v>
       </c>
       <c r="H3" s="1">
-        <v>38.24</v>
+        <v>5.88</v>
       </c>
       <c r="I3" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1424,25 +1436,25 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>75.61</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>24.39</v>
+        <v>9.76</v>
       </c>
       <c r="I4" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1456,28 +1468,28 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>78.05</v>
+        <v>87.5</v>
       </c>
       <c r="H5" s="1">
-        <v>21.95</v>
+        <v>12.5</v>
       </c>
       <c r="I5" s="2">
         <v>8</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1494,25 +1506,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H6" s="1">
-        <v>8.33</v>
+        <v>2.78</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1561,19 +1573,19 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>26</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>83.87</v>
+        <v>86.67</v>
       </c>
       <c r="H8" s="1">
-        <v>16.13</v>
+        <v>13.33</v>
       </c>
       <c r="I8" s="2">
         <v>6.9</v>
@@ -1701,22 +1713,22 @@
         <v>24</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12">
         <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>83.33</v>
+        <v>83.72</v>
       </c>
       <c r="H12" s="1">
-        <v>16.67</v>
+        <v>16.28</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Química - Estadisticos 20221.xlsx
+++ b/academias/Química - Estadisticos 20221.xlsx
@@ -1122,22 +1122,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1154,22 +1157,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>86.67</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>13.33</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.6</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1186,22 +1192,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.9</v>
       </c>
       <c r="J9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1218,22 +1227,25 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F10">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J10">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1250,22 +1262,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>86.05</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>13.95</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1282,22 +1297,25 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>20.93</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.8</v>
       </c>
       <c r="J12">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1541,19 +1559,19 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H7" s="1">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I7" s="2">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1588,7 +1606,7 @@
         <v>13.33</v>
       </c>
       <c r="I8" s="2">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1611,19 +1629,19 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="H9" s="1">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1658,7 +1676,7 @@
         <v>4.55</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1693,7 +1711,7 @@
         <v>13.95</v>
       </c>
       <c r="I11" s="2">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1716,19 +1734,19 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>83.72</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>16.28</v>
+        <v>20.93</v>
       </c>
       <c r="I12" s="2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Química - Estadisticos 20221.xlsx
+++ b/academias/Química - Estadisticos 20221.xlsx
@@ -1020,22 +1020,25 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>85.37</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>14.63</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1052,25 +1055,25 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H5" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1454,16 +1457,16 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>90.23999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="H4" s="1">
-        <v>9.76</v>
+        <v>14.63</v>
       </c>
       <c r="I4" s="2">
         <v>7.8</v>
@@ -1489,19 +1492,19 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="H5" s="1">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>

--- a/academias/Química - Estadisticos 20221.xlsx
+++ b/academias/Química - Estadisticos 20221.xlsx
@@ -1387,19 +1387,19 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>82.05</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>17.95</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1422,19 +1422,19 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H3" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1492,19 +1492,19 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>85</v>
+        <v>97.5</v>
       </c>
       <c r="H5" s="1">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="I5" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1527,16 +1527,16 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>8</v>

--- a/academias/Química - Estadisticos 20221.xlsx
+++ b/academias/Química - Estadisticos 20221.xlsx
@@ -1457,19 +1457,19 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>85.37</v>
+        <v>95.12</v>
       </c>
       <c r="H4" s="1">
-        <v>14.63</v>
+        <v>4.88</v>
       </c>
       <c r="I4" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>0</v>

--- a/academias/Química - Estadisticos 20221.xlsx
+++ b/academias/Química - Estadisticos 20221.xlsx
@@ -1609,7 +1609,7 @@
         <v>13.33</v>
       </c>
       <c r="I8" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
         <v>0</v>

--- a/academias/Química - Estadisticos 20221.xlsx
+++ b/academias/Química - Estadisticos 20221.xlsx
@@ -1644,7 +1644,7 @@
         <v>12.5</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1702,19 +1702,19 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>86.05</v>
+        <v>88.37</v>
       </c>
       <c r="H11" s="1">
-        <v>13.95</v>
+        <v>11.63</v>
       </c>
       <c r="I11" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1737,19 +1737,19 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>79.06999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H12" s="1">
-        <v>20.93</v>
+        <v>13.95</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
         <v>0</v>
